--- a/artfynd/A 39595-2024 artfynd.xlsx
+++ b/artfynd/A 39595-2024 artfynd.xlsx
@@ -1199,7 +1199,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119709991</v>
+        <v>119710025</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1247,17 +1247,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gullsjötorp knärot no, Srm</t>
+          <t>Gullsjötorp, knärot 150 m o, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603245</v>
+        <v>603191</v>
       </c>
       <c r="R6" t="n">
-        <v>6547503</v>
+        <v>6547483</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1277,6 +1277,11 @@
       <c r="W6" t="inlineStr">
         <is>
           <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D-Fle-0186</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1318,7 +1323,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119710025</v>
+        <v>119709991</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1353,7 +1358,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1366,17 +1371,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gullsjötorp, knärot 150 m o, Srm</t>
+          <t>Gullsjötorp knärot no, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603191</v>
+        <v>603245</v>
       </c>
       <c r="R7" t="n">
-        <v>6547483</v>
+        <v>6547503</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1396,11 +1401,6 @@
       <c r="W7" t="inlineStr">
         <is>
           <t>Helgesta</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>D-Fle-0186</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">

--- a/artfynd/A 39595-2024 artfynd.xlsx
+++ b/artfynd/A 39595-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1197,249 +1197,6 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>119710025</v>
-      </c>
-      <c r="B6" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Gullsjötorp, knärot 150 m o, Srm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>603191</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6547483</v>
-      </c>
-      <c r="S6" t="n">
-        <v>25</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Flen</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Helgesta</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>D-Fle-0186</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>119709991</v>
-      </c>
-      <c r="B7" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Gullsjötorp knärot no, Srm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>603245</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6547503</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Flen</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Helgesta</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
